--- a/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
   <si>
     <t>ALXO</t>
   </si>
@@ -656,113 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -806,34 +809,37 @@
         <v>0</v>
       </c>
       <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
         <v>500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1200</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1300</v>
       </c>
       <c r="U8" s="3">
         <v>1300</v>
       </c>
       <c r="V8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="W8" s="3">
         <v>1000</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -876,35 +882,38 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3">
         <v>500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>600</v>
-      </c>
-      <c r="S9" s="3">
-        <v>1100</v>
       </c>
       <c r="T9" s="3">
         <v>1100</v>
       </c>
       <c r="U9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V9" s="3">
         <v>1200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>900</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,26 +956,26 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S10" s="3">
         <v>100</v>
       </c>
       <c r="T10" s="3">
+        <v>100</v>
+      </c>
+      <c r="U10" s="3">
         <v>200</v>
-      </c>
-      <c r="U10" s="3">
-        <v>100</v>
       </c>
       <c r="V10" s="3">
         <v>100</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
+      <c r="W10" s="3">
+        <v>100</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
@@ -974,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,79 +1013,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E12" s="3">
         <v>45800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>29500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>24800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>25200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>29400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>17100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>20900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3700</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,8 +1159,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1157,11 +1176,11 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1169,11 +1188,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -1181,12 +1200,12 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1202,8 +1221,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1214,8 +1233,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1285,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,79 +1334,83 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E17" s="3">
         <v>53300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>36800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>32200</v>
       </c>
       <c r="G17" s="3">
         <v>32200</v>
       </c>
       <c r="H17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="I17" s="3">
         <v>36700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>33800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5300</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1389,70 +1418,73 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-53300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-36800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-32200</v>
       </c>
       <c r="G18" s="3">
         <v>-32200</v>
       </c>
       <c r="H18" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-36700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-33800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-24700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-28500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-18400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4300</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,8 +1510,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1487,26 +1520,26 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F20" s="3">
         <v>3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1520,14 +1553,14 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1540,8 +1573,8 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1549,8 +1582,11 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1558,61 +1594,61 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-33600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-29600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-30500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-35200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-32800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-24500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-28400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-24600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-14200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-18400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-11000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2900</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-4100</v>
       </c>
       <c r="V21" s="3">
         <v>-4100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
+      <c r="W21" s="3">
+        <v>-4100</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
@@ -1620,8 +1656,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1634,11 +1673,11 @@
       <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="G22" s="3">
+        <v>400</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1659,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P22" s="3">
         <v>200</v>
@@ -1671,19 +1710,19 @@
         <v>200</v>
       </c>
       <c r="S22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
@@ -1691,70 +1730,73 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-51000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-34200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-30200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-30600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-35300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-32900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-11300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3000</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-4200</v>
       </c>
       <c r="V23" s="3">
         <v>-4200</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
+      <c r="W23" s="3">
+        <v>-4200</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
@@ -1762,13 +1804,16 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
@@ -1776,20 +1821,20 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1801,11 +1846,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1824,8 +1869,8 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
@@ -1833,8 +1878,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,70 +1952,73 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-51000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-30200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-30700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-35300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-32900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-24500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-11300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3000</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-4200</v>
       </c>
       <c r="V26" s="3">
         <v>-4200</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+      <c r="W26" s="3">
+        <v>-4200</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
@@ -1975,79 +2026,85 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-51000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-30200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-30700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-35300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-32900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-24500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5100</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,8 +2396,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2339,26 +2408,26 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2372,14 +2441,14 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2392,8 +2461,8 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2401,79 +2470,85 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-51000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-30200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-30700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-35300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-32900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-24500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5100</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-51000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-30200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-30700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-35300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-32900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-24500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5100</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,59 +2829,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E41" s="3">
         <v>19600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>38000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>63200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>48800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>66400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>159100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>363700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>385100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>410000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>429900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>434200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>259500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>98100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>105000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,35 +2901,38 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>160300</v>
+      </c>
+      <c r="E42" s="3">
         <v>170400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>174800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>164800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>217400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>235900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>247000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>157500</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2859,8 +2948,8 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2886,23 +2975,26 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2912,8 +3004,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2928,17 +3020,17 @@
         <v>0</v>
       </c>
       <c r="P43" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="3">
         <v>500</v>
       </c>
       <c r="R43" s="3">
+        <v>500</v>
+      </c>
+      <c r="S43" s="3">
         <v>1200</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2957,8 +3049,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3028,59 +3123,62 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E45" s="3">
         <v>8500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3099,59 +3197,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>188700</v>
+      </c>
+      <c r="E46" s="3">
         <v>199100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>219600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>232500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>271000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>290800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>316800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>321500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>367000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>389000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>412300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>432300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>436000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>262400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>100700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>107400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,35 +3271,38 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E47" s="3">
         <v>6400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>16700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>25100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3214,8 +3318,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3241,59 +3345,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E48" s="3">
         <v>9800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>3400</v>
       </c>
       <c r="L48" s="3">
         <v>3400</v>
       </c>
       <c r="M48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="N48" s="3">
         <v>200</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
       <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
         <v>100</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
       <c r="Q48" s="3">
         <v>0</v>
       </c>
       <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
         <v>800</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3312,8 +3419,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3383,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,59 +3641,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E52" s="3">
         <v>4800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>10100</v>
       </c>
       <c r="J52" s="3">
         <v>10100</v>
       </c>
       <c r="K52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="L52" s="3">
         <v>9800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>500</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>2400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3596,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,59 +3789,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>242600</v>
+      </c>
+      <c r="E54" s="3">
         <v>220100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>245900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>278100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>306500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>317700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>346000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>363700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>380200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>399700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>421300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>432900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>436100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>262400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>103100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>108400</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,59 +3921,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E57" s="3">
         <v>13000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7400</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,25 +3993,28 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>700</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>400</v>
       </c>
       <c r="I58" s="3">
         <v>400</v>
@@ -3899,23 +4032,23 @@
         <v>400</v>
       </c>
       <c r="N58" s="3">
+        <v>400</v>
+      </c>
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
         <v>2600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>900</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,59 +4067,62 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E59" s="3">
         <v>22100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4005,59 +4141,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E60" s="3">
         <v>35100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24000</v>
-      </c>
-      <c r="J60" s="3">
-        <v>15300</v>
       </c>
       <c r="K60" s="3">
         <v>15300</v>
       </c>
       <c r="L60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="M60" s="3">
         <v>12500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4076,59 +4215,62 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E61" s="3">
         <v>9600</v>
-      </c>
-      <c r="E61" s="3">
-        <v>9500</v>
       </c>
       <c r="F61" s="3">
         <v>9500</v>
       </c>
       <c r="G61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="H61" s="3">
         <v>9400</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>3200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4700</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4147,59 +4289,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E62" s="3">
         <v>6600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
       <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,59 +4585,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E66" s="3">
         <v>51400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>37800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>43000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>30700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9300</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4716,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3">
         <v>175000</v>
       </c>
       <c r="S70" s="3">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
@@ -4742,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,59 +4983,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-486300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-440800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-389800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-355700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-325500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-294800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-259400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-226500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-202000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-173500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-149000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-132700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-118500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-99700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-89600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-78200</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4884,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,59 +5279,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>189700</v>
+      </c>
+      <c r="E76" s="3">
         <v>168800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>212700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>240400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>263500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>287000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>316300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>343600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>363000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>385200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>405000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>418500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>429800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>252000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-84400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-75900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5168,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-51000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-30200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-30700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-35300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-32900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-24500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5100</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,8 +5610,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5428,7 +5626,7 @@
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -5440,7 +5638,7 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -5458,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
@@ -5475,8 +5673,8 @@
       <c r="V83" s="3">
         <v>100</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>100</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -5484,8 +5682,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6052,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-31200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-31700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-27800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-20700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-30900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-17000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-20700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-20600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,41 +6156,42 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -5988,28 +6208,31 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,41 +6376,44 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E94" s="3">
         <v>12800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>6200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>42300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>10900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>13700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-76100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-183900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -6192,37 +6421,40 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>600</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6319,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,70 +6774,73 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>188400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>170300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>105000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>9400</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
+      <c r="W100" s="3">
+        <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
@@ -6603,8 +6848,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6674,75 +6922,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-25200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-92700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-204500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-21500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-24800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>174700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>161400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>96000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4000</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
   <si>
     <t>ALXO</t>
   </si>
@@ -656,116 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -812,34 +816,37 @@
         <v>0</v>
       </c>
       <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
         <v>500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1200</v>
-      </c>
-      <c r="U8" s="3">
-        <v>1300</v>
       </c>
       <c r="V8" s="3">
         <v>1300</v>
       </c>
       <c r="W8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X8" s="3">
         <v>1000</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -885,35 +892,38 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3">
         <v>500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>600</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1100</v>
       </c>
       <c r="U9" s="3">
         <v>1100</v>
       </c>
       <c r="V9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W9" s="3">
         <v>1200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>900</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -959,26 +969,26 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3">
-        <v>0</v>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T10" s="3">
         <v>100</v>
       </c>
       <c r="U10" s="3">
+        <v>100</v>
+      </c>
+      <c r="V10" s="3">
         <v>200</v>
-      </c>
-      <c r="V10" s="3">
-        <v>100</v>
       </c>
       <c r="W10" s="3">
         <v>100</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
+      <c r="X10" s="3">
+        <v>100</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
@@ -986,8 +996,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,82 +1027,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E12" s="3">
         <v>41800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>45800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>29500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>25200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3700</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,40 +1179,43 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
@@ -1203,12 +1223,12 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1224,8 +1244,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1236,8 +1256,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1310,8 +1333,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,82 +1361,86 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E17" s="3">
         <v>48000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>53300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>36800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>32200</v>
       </c>
       <c r="H17" s="3">
         <v>32200</v>
       </c>
       <c r="I17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="J17" s="3">
         <v>36700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>33800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5300</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1418,73 +1448,76 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-53300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-36800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-32200</v>
       </c>
       <c r="H18" s="3">
         <v>-32200</v>
       </c>
       <c r="I18" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="J18" s="3">
         <v>-36700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-33800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-24700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-28500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-24600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-14200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-10800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-4300</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,8 +1544,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1520,29 +1554,29 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F20" s="3">
         <v>2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1556,14 +1590,14 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1576,8 +1610,8 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
@@ -1585,8 +1619,11 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1594,64 +1631,64 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-44900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-50400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-33600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-29600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-30500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-35200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-32800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-24500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-28400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-24600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-16300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-14200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-11000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2900</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-4100</v>
       </c>
       <c r="W21" s="3">
         <v>-4100</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
+      <c r="X21" s="3">
+        <v>-4100</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
@@ -1659,8 +1696,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1676,11 +1716,11 @@
       <c r="G22" s="3">
         <v>400</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="H22" s="3">
+        <v>400</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1701,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>200</v>
@@ -1713,19 +1753,19 @@
         <v>200</v>
       </c>
       <c r="T22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
@@ -1733,73 +1773,76 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-45500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-51000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-34200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-30200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-30600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-35300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-32900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3000</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-4200</v>
       </c>
       <c r="W23" s="3">
         <v>-4200</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
+      <c r="X23" s="3">
+        <v>-4200</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
@@ -1807,16 +1850,19 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1824,20 +1870,20 @@
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1849,11 +1895,11 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1872,8 +1918,8 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
+      <c r="X24" s="3">
+        <v>0</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
@@ -1881,8 +1927,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,73 +2004,76 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-45500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-51000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-34200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-30200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-30700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-35300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-32900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-24500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-28400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-16300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-11300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3000</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-4200</v>
       </c>
       <c r="W26" s="3">
         <v>-4200</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
+      <c r="X26" s="3">
+        <v>-4200</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
@@ -2029,82 +2081,88 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-45500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-51000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-30200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-30700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-35300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-32900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-24500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-28400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5100</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,8 +2466,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2408,29 +2478,29 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2444,14 +2514,14 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2464,8 +2534,8 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
@@ -2473,82 +2543,88 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-45500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-51000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-34200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-30200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-30700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-35300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-32900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-24500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-28400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-24600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5100</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-45500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-51000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-34200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-30200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-30700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-35300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-32900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-24500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-28400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-24600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5100</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,62 +2916,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E41" s="3">
         <v>22400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>38000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>63200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>48800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>66400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>159100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>363700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>385100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>410000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>429900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>434200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>259500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>98100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>105000</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,38 +2991,41 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>143400</v>
+      </c>
+      <c r="E42" s="3">
         <v>160300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>170400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>174800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>164800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>217400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>235900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>247000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>157500</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2951,8 +3041,8 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2978,26 +3068,29 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3007,8 +3100,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3023,17 +3116,17 @@
         <v>0</v>
       </c>
       <c r="Q43" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="R43" s="3">
         <v>500</v>
       </c>
       <c r="S43" s="3">
+        <v>500</v>
+      </c>
+      <c r="T43" s="3">
         <v>1200</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3052,8 +3145,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3126,62 +3222,65 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E45" s="3">
         <v>4900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1200</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,62 +3299,65 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>167900</v>
+      </c>
+      <c r="E46" s="3">
         <v>188700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>199100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>219600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>232500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>271000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>290800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>316800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>321500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>367000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>389000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>412300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>432300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>436000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>262400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>100700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>107400</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,38 +3376,41 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E47" s="3">
         <v>35400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>28200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>25100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3321,8 +3426,8 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3348,62 +3453,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E48" s="3">
         <v>10800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>3400</v>
       </c>
       <c r="M48" s="3">
         <v>3400</v>
       </c>
       <c r="N48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="O48" s="3">
         <v>200</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
       <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
       <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
         <v>800</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3422,8 +3530,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3496,8 +3607,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,62 +3761,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E52" s="3">
         <v>7600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>10100</v>
       </c>
       <c r="K52" s="3">
         <v>10100</v>
       </c>
       <c r="L52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="M52" s="3">
         <v>9800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>500</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>2400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3718,8 +3838,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,62 +3915,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>212700</v>
+      </c>
+      <c r="E54" s="3">
         <v>242600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>220100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>245900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>278100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>306500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>317700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>346000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>363700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>380200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>399700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>421300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>432900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>436100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>262400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>103100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>108400</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3992,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,62 +4052,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E57" s="3">
         <v>8600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7400</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2000</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,28 +4127,31 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>900</v>
+      </c>
+      <c r="E58" s="3">
         <v>700</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>400</v>
       </c>
       <c r="J58" s="3">
         <v>400</v>
@@ -4035,23 +4169,23 @@
         <v>400</v>
       </c>
       <c r="O58" s="3">
+        <v>400</v>
+      </c>
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>2600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>900</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,62 +4204,65 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E59" s="3">
         <v>26700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4144,62 +4281,65 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E60" s="3">
         <v>36000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>35100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>24000</v>
-      </c>
-      <c r="K60" s="3">
-        <v>15300</v>
       </c>
       <c r="L60" s="3">
         <v>15300</v>
       </c>
       <c r="M60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="N60" s="3">
         <v>12500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4000</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,62 +4358,65 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E61" s="3">
         <v>11200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9600</v>
-      </c>
-      <c r="F61" s="3">
-        <v>9500</v>
       </c>
       <c r="G61" s="3">
         <v>9500</v>
       </c>
       <c r="H61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="I61" s="3">
         <v>9400</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>3200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4700</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4292,62 +4435,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E62" s="3">
         <v>5600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>200</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4366,8 +4512,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,62 +4743,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E66" s="3">
         <v>52800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>51400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>37800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>43000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>29700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9300</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,8 +4820,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4886,13 +5054,13 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="S70" s="3">
         <v>175000</v>
       </c>
       <c r="T70" s="3">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="U70" s="3">
         <v>0</v>
@@ -4912,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,62 +5157,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-521900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-486300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-440800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-389800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-355700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-325500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-294800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-259400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-226500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-202000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-173500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-149000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-132700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-118500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-99700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-89600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-78200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5060,8 +5234,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,62 +5465,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>164200</v>
+      </c>
+      <c r="E76" s="3">
         <v>189700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>168800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>212700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>240400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>263500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>287000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>316300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>343600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>363000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>385200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>405000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>418500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>429800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>252000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-84400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-75900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,8 +5542,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-45500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-51000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-34200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-30200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-30700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-35300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-32900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-24500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-28400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-24600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5100</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,8 +5809,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5629,7 +5828,7 @@
         <v>200</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -5641,7 +5840,7 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -5659,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="R83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S83" s="3">
         <v>100</v>
@@ -5676,8 +5875,8 @@
       <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>100</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
@@ -5685,8 +5884,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,82 +6269,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-37900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-39700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-31200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-31700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-20700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-30900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-20700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-24900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-20600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3900</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,8 +6377,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6166,35 +6387,35 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -6211,28 +6432,31 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,44 +6606,47 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-16700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>12800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>6200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>42300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>10900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>13700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-76100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-183900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-400</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -6424,37 +6654,40 @@
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>600</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6714,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6555,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,73 +7020,76 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E100" s="3">
         <v>59200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>188400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>170300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>105000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5900</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>9400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
+      <c r="X100" s="3">
+        <v>0</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
@@ -6851,8 +7097,11 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6925,78 +7174,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E102" s="3">
         <v>2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-25200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>14400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-92700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-204500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-21500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-24800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>174700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>161400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>96000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4000</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
   <si>
     <t>ALXO</t>
   </si>
@@ -656,120 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -819,34 +823,37 @@
         <v>0</v>
       </c>
       <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1200</v>
-      </c>
-      <c r="V8" s="3">
-        <v>1300</v>
       </c>
       <c r="W8" s="3">
         <v>1300</v>
       </c>
       <c r="X8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Y8" s="3">
         <v>1000</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -895,35 +902,38 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3">
         <v>500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>600</v>
-      </c>
-      <c r="U9" s="3">
-        <v>1100</v>
       </c>
       <c r="V9" s="3">
         <v>1100</v>
       </c>
       <c r="W9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X9" s="3">
         <v>1200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>900</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -972,26 +982,26 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U10" s="3">
         <v>100</v>
       </c>
       <c r="V10" s="3">
+        <v>100</v>
+      </c>
+      <c r="W10" s="3">
         <v>200</v>
-      </c>
-      <c r="W10" s="3">
-        <v>100</v>
       </c>
       <c r="X10" s="3">
         <v>100</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
+      <c r="Y10" s="3">
+        <v>100</v>
       </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
@@ -999,8 +1009,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,85 +1041,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E12" s="3">
         <v>31700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>41800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>45800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>29500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>25200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>29400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>18200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3700</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,8 +1199,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1208,17 +1228,17 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
@@ -1226,12 +1246,12 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1247,8 +1267,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1259,8 +1279,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1336,8 +1359,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,85 +1388,89 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>41500</v>
+      </c>
+      <c r="E17" s="3">
         <v>37800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>53300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>36800</v>
-      </c>
-      <c r="H17" s="3">
-        <v>32200</v>
       </c>
       <c r="I17" s="3">
         <v>32200</v>
       </c>
       <c r="J17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="K17" s="3">
         <v>36700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>33800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5300</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1448,76 +1478,79 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-48000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-53300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-36800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-32200</v>
       </c>
       <c r="I18" s="3">
         <v>-32200</v>
       </c>
       <c r="J18" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-36700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-33800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-28500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-18400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-4200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,8 +1578,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1554,32 +1588,32 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F20" s="3">
         <v>3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1593,14 +1627,14 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1613,8 +1647,8 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="Y20" s="3">
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
@@ -1622,8 +1656,11 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1631,67 +1668,67 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-44900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-50400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-33600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-29600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-30500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-35200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-32800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-24500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-28400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-24600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-18400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-11000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2900</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-4100</v>
       </c>
       <c r="X21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
+      <c r="Y21" s="3">
+        <v>-4100</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
@@ -1699,8 +1736,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1719,11 +1759,11 @@
       <c r="H22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="I22" s="3">
+        <v>400</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1744,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R22" s="3">
         <v>200</v>
@@ -1756,19 +1796,19 @@
         <v>200</v>
       </c>
       <c r="U22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -1776,76 +1816,79 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-35600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-45500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-51000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-34200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-30200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-30600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-35300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-32900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-7800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3000</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-4200</v>
       </c>
       <c r="X23" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
+      <c r="Y23" s="3">
+        <v>-4200</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
@@ -1853,19 +1896,22 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1873,20 +1919,20 @@
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1898,11 +1944,11 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1921,8 +1967,8 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
+      <c r="Y24" s="3">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
@@ -1930,8 +1976,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,76 +2056,79 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-35600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-45500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-51000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-34200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-30200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-30700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-35300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-32900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-24600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-16300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3000</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-4200</v>
       </c>
       <c r="X26" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
+      <c r="Y26" s="3">
+        <v>-4200</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
@@ -2084,85 +2136,91 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-35600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-45500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-51000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-34200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-30200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-30700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-35300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-32900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-24600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-16300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-14000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2296,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,8 +2376,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2456,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,8 +2536,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2478,32 +2548,32 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2517,14 +2587,14 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2537,8 +2607,8 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="Y32" s="3">
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
@@ -2546,85 +2616,91 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-35600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-45500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-51000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-34200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-30200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-30700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-35300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-32900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-24600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-16300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-14000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2776,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-35600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-45500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-51000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-34200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-30200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-30700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-35300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-32900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-24600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-16300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-14000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2973,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,65 +3003,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E41" s="3">
         <v>14000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>38000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>63200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>48800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>159100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>363700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>385100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>410000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>429900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>434200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>259500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>98100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>105000</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,41 +3081,44 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>141200</v>
+      </c>
+      <c r="E42" s="3">
         <v>143400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>160300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>170400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>174800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>164800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>217400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>235900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>247000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>157500</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3044,8 +3134,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3071,29 +3161,32 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>800</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3103,8 +3196,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3119,17 +3212,17 @@
         <v>0</v>
       </c>
       <c r="R43" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="S43" s="3">
         <v>500</v>
       </c>
       <c r="T43" s="3">
+        <v>500</v>
+      </c>
+      <c r="U43" s="3">
         <v>1200</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3148,8 +3241,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3225,65 +3321,68 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E45" s="3">
         <v>9300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,65 +3401,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>168700</v>
+      </c>
+      <c r="E46" s="3">
         <v>167900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>188700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>199100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>219600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>232500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>271000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>290800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>316800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>321500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>367000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>389000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>412300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>432300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>436000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>262400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>100700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>107400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,41 +3481,44 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E47" s="3">
         <v>27000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>35400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>28200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>16700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>25100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3429,8 +3534,8 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -3456,65 +3561,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E48" s="3">
         <v>10200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>3400</v>
       </c>
       <c r="N48" s="3">
         <v>3400</v>
       </c>
       <c r="O48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="P48" s="3">
         <v>200</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
       <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
         <v>100</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
       <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3">
         <v>800</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,8 +3641,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3610,8 +3721,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3801,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,65 +3881,68 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E52" s="3">
         <v>7500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>10100</v>
       </c>
       <c r="L52" s="3">
         <v>10100</v>
       </c>
       <c r="M52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="N52" s="3">
         <v>9800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>500</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>2400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3841,8 +3961,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,65 +4041,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>214600</v>
+      </c>
+      <c r="E54" s="3">
         <v>212700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>242600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>220100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>245900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>278100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>306500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>317700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>346000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>363700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>380200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>399700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>421300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>432900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>436100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>262400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>103100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>108400</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4121,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4153,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,65 +4183,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E57" s="3">
         <v>6200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7400</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4130,31 +4261,34 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
         <v>900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>700</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>400</v>
       </c>
       <c r="K58" s="3">
         <v>400</v>
@@ -4172,23 +4306,23 @@
         <v>400</v>
       </c>
       <c r="P58" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
         <v>2600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>900</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4207,65 +4341,68 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E59" s="3">
         <v>25100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,65 +4421,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E60" s="3">
         <v>32200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>21900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>25200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24000</v>
-      </c>
-      <c r="L60" s="3">
-        <v>15300</v>
       </c>
       <c r="M60" s="3">
         <v>15300</v>
       </c>
       <c r="N60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="O60" s="3">
         <v>12500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4000</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,65 +4501,68 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E61" s="3">
         <v>10900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9600</v>
-      </c>
-      <c r="G61" s="3">
-        <v>9500</v>
       </c>
       <c r="H61" s="3">
         <v>9500</v>
       </c>
       <c r="I61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="J61" s="3">
         <v>9400</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>3200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4700</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4438,65 +4581,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E62" s="3">
         <v>5400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>200</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
         <v>800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>600</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4515,8 +4661,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4741,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4821,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,65 +4901,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E66" s="3">
         <v>48500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>52800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>51400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>43000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>29700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9300</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4981,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5013,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5091,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5171,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5057,13 +5225,13 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>175000</v>
       </c>
       <c r="U70" s="3">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="V70" s="3">
         <v>0</v>
@@ -5083,8 +5251,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,65 +5331,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-561300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-521900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-486300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-440800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-389800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-355700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-325500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-294800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-259400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-226500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-202000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-173500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-149000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-132700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-118500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-99700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-89600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-78200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5237,8 +5411,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5491,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5571,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,65 +5651,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>159300</v>
+      </c>
+      <c r="E76" s="3">
         <v>164200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>189700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>168800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>212700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>240400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>263500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>287000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>316300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>343600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>363000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>385200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>405000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>418500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>429800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>252000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-84400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-75900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5731,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5811,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-35600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-45500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-51000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-34200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-30200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-30700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-35300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-32900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-24600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-16300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-14000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,8 +6008,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5831,7 +6030,7 @@
         <v>200</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -5843,7 +6042,7 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -5861,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
@@ -5878,8 +6077,8 @@
       <c r="X83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>100</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
@@ -5887,8 +6086,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6166,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6246,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6326,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6406,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,85 +6486,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-37900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-39700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-31200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-31700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-27800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-20700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-20700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-17500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-24900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-20600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-13600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-9000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,8 +6598,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6390,35 +6611,35 @@
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -6435,28 +6656,31 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6756,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,47 +6836,50 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>900</v>
+      </c>
+      <c r="E94" s="3">
         <v>26500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>12800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>6200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>42300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>10900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>13700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-76100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-183900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -6657,37 +6887,40 @@
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>600</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +6948,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6792,8 +7026,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7106,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7186,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,76 +7266,79 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E100" s="3">
         <v>3100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>59200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>188400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>170300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>105000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5900</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>9400</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
+      <c r="Y100" s="3">
+        <v>0</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
@@ -7100,8 +7346,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7177,81 +7426,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-25200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-92700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-204500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-24800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>174700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>161400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>96000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>ALXO</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -826,34 +830,37 @@
         <v>0</v>
       </c>
       <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1200</v>
-      </c>
-      <c r="W8" s="3">
-        <v>1300</v>
       </c>
       <c r="X8" s="3">
         <v>1300</v>
       </c>
       <c r="Y8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z8" s="3">
         <v>1000</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -905,35 +912,38 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3">
         <v>500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>600</v>
-      </c>
-      <c r="V9" s="3">
-        <v>1100</v>
       </c>
       <c r="W9" s="3">
         <v>1100</v>
       </c>
       <c r="X9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y9" s="3">
         <v>1200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>900</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -985,26 +995,26 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V10" s="3">
         <v>100</v>
       </c>
       <c r="W10" s="3">
+        <v>100</v>
+      </c>
+      <c r="X10" s="3">
         <v>200</v>
-      </c>
-      <c r="X10" s="3">
-        <v>100</v>
       </c>
       <c r="Y10" s="3">
         <v>100</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
+      <c r="Z10" s="3">
+        <v>100</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
@@ -1012,8 +1022,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1042,88 +1055,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E12" s="3">
         <v>34700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>41800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>45800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>29500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>24800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>18200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>9800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3700</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1202,46 +1219,49 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1249,12 +1269,12 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,8 +1290,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1282,31 +1302,34 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1362,8 +1385,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1389,168 +1415,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E17" s="3">
         <v>41500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>37800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>53300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>36800</v>
-      </c>
-      <c r="I17" s="3">
-        <v>32200</v>
       </c>
       <c r="J17" s="3">
         <v>32200</v>
       </c>
       <c r="K17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="L17" s="3">
         <v>36700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>33800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5300</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-32600</v>
       </c>
       <c r="E18" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-37800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-48000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-53300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-36800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-32200</v>
       </c>
       <c r="J18" s="3">
         <v>-32200</v>
       </c>
       <c r="K18" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="L18" s="3">
         <v>-36700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-33800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-24700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-28500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-18400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1579,44 +1612,45 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>2400</v>
+        <v>-300</v>
       </c>
       <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
         <v>1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1630,14 +1664,14 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1650,8 +1684,8 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
+      <c r="Z20" s="3">
+        <v>0</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
@@ -1659,79 +1693,82 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-32300</v>
       </c>
       <c r="E21" s="3">
-        <v>-34900</v>
+        <v>-40900</v>
       </c>
       <c r="F21" s="3">
-        <v>-44900</v>
+        <v>-37600</v>
       </c>
       <c r="G21" s="3">
-        <v>-50400</v>
+        <v>-47800</v>
       </c>
       <c r="H21" s="3">
-        <v>-33600</v>
+        <v>-53100</v>
       </c>
       <c r="I21" s="3">
-        <v>-29600</v>
+        <v>-36000</v>
       </c>
       <c r="J21" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-30500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-35200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-32800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-24500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-28400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-24600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-14200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-18400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-11000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2900</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-4100</v>
       </c>
       <c r="Y21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
+      <c r="Z21" s="3">
+        <v>-4100</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
@@ -1739,8 +1776,11 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1762,11 +1802,11 @@
       <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="J22" s="3">
+        <v>400</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1787,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3">
         <v>200</v>
@@ -1799,19 +1839,19 @@
         <v>200</v>
       </c>
       <c r="V22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
@@ -1819,79 +1859,82 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-39400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-35600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-45500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-51000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-34200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-30200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-30600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-35300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-32900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-18600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-7800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3000</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-4200</v>
       </c>
       <c r="Y23" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
+      <c r="Z23" s="3">
+        <v>-4200</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
@@ -1899,8 +1942,11 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1910,8 +1956,8 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1922,20 +1968,20 @@
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1947,11 +1993,11 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -1970,8 +2016,8 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
@@ -1979,8 +2025,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2059,79 +2108,82 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-39400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-35600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-45500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-51000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-34200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-30200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-30700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-35300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-32900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-18800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3000</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-4200</v>
       </c>
       <c r="Y26" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
+      <c r="Z26" s="3">
+        <v>-4200</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
@@ -2139,88 +2191,94 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-39400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-35600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-45500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-51000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-34200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-30200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-30700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-35300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-32900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-24600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-18800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-14000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2299,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2379,8 +2440,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2459,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2539,44 +2606,47 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-2600</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-2700</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-2400</v>
+        <v>300</v>
       </c>
       <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2590,14 +2660,14 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2610,8 +2680,8 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
+      <c r="Z32" s="3">
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
@@ -2619,88 +2689,94 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-39400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-35600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-45500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-51000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-34200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-30200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-30700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-35300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-32900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-24500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-24600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-18800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-14000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2779,173 +2855,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-39400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-35600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-45500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-51000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-34200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-30200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-30700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-35300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-32900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-24500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-24600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-18800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-14000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2974,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3004,68 +3090,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E41" s="3">
         <v>15500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>38000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>63200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>48800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>49100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>66400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>159100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>363700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>385100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>410000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>429900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>434200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>259500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>98100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>105000</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3084,44 +3171,47 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>132500</v>
+      </c>
+      <c r="E42" s="3">
         <v>141200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>143400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>160300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>170400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>174800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>164800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>217400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>235900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>247000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>157500</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3137,8 +3227,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3164,8 +3254,11 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3173,23 +3266,23 @@
         <v>1200</v>
       </c>
       <c r="E43" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F43" s="3">
         <v>1100</v>
       </c>
-      <c r="F43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>800</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,8 +3292,8 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -3215,17 +3308,17 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="T43" s="3">
         <v>500</v>
       </c>
       <c r="U43" s="3">
+        <v>500</v>
+      </c>
+      <c r="V43" s="3">
         <v>1200</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3244,31 +3337,34 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3324,68 +3420,71 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>10800</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E45" s="3">
-        <v>9300</v>
-      </c>
-      <c r="F45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="L45" s="3">
+        <v>5900</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N45" s="3">
         <v>4900</v>
       </c>
-      <c r="G45" s="3">
-        <v>8500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>6200</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="O45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="P45" s="3">
         <v>3800</v>
       </c>
-      <c r="J45" s="3">
-        <v>4800</v>
-      </c>
-      <c r="K45" s="3">
-        <v>5900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>4900</v>
-      </c>
-      <c r="N45" s="3">
-        <v>3400</v>
-      </c>
-      <c r="O45" s="3">
-        <v>3800</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1200</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3404,68 +3503,71 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>155900</v>
+      </c>
+      <c r="E46" s="3">
         <v>168700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>167900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>188700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>199100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>219600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>232500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>271000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>290800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>316800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>321500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>367000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>389000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>412300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>432300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>436000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>262400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>100700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>107400</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3484,44 +3586,47 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E47" s="3">
         <v>29500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>27000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>35400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>28200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>16700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>25100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3642,8 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -3564,68 +3669,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E48" s="3">
         <v>10700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>3400</v>
       </c>
       <c r="O48" s="3">
         <v>3400</v>
       </c>
       <c r="P48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Q48" s="3">
         <v>200</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
       <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
         <v>100</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
       <c r="U48" s="3">
+        <v>0</v>
+      </c>
+      <c r="V48" s="3">
         <v>800</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3644,8 +3752,11 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3724,8 +3835,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3804,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3884,68 +4001,71 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E52" s="3">
         <v>5700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>10100</v>
       </c>
       <c r="M52" s="3">
         <v>10100</v>
       </c>
       <c r="N52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="O52" s="3">
         <v>9800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>500</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>2400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3964,8 +4084,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4044,68 +4167,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>185700</v>
+      </c>
+      <c r="E54" s="3">
         <v>214600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>212700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>242600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>220100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>245900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>278100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>306500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>317700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>346000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>363700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>380200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>399700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>421300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>432900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>436100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>262400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>103100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>108400</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4250,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4154,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4184,68 +4314,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E57" s="3">
         <v>8100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7400</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
         <v>1400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2000</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4264,34 +4395,37 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="E58" s="3">
-        <v>900</v>
-      </c>
-      <c r="F58" s="3">
-        <v>700</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="J58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K58" s="3">
         <v>300</v>
-      </c>
-      <c r="K58" s="3">
-        <v>400</v>
       </c>
       <c r="L58" s="3">
         <v>400</v>
@@ -4309,23 +4443,23 @@
         <v>400</v>
       </c>
       <c r="Q58" s="3">
+        <v>400</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
         <v>2600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>900</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4344,68 +4478,71 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>29500</v>
+        <v>7700</v>
       </c>
       <c r="E59" s="3">
-        <v>25100</v>
+        <v>13400</v>
       </c>
       <c r="F59" s="3">
-        <v>26700</v>
+        <v>9900</v>
       </c>
       <c r="G59" s="3">
-        <v>22100</v>
+        <v>10400</v>
       </c>
       <c r="H59" s="3">
-        <v>13500</v>
+        <v>12700</v>
       </c>
       <c r="I59" s="3">
-        <v>11900</v>
+        <v>2700</v>
       </c>
       <c r="J59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K59" s="3">
         <v>20000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1100</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4424,68 +4561,71 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E60" s="3">
         <v>38400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>36000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>25200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24000</v>
-      </c>
-      <c r="M60" s="3">
-        <v>15300</v>
       </c>
       <c r="N60" s="3">
         <v>15300</v>
       </c>
       <c r="O60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="P60" s="3">
         <v>12500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4000</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4504,68 +4644,71 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11800</v>
+        <v>15500</v>
       </c>
       <c r="E61" s="3">
-        <v>10900</v>
+        <v>15700</v>
       </c>
       <c r="F61" s="3">
-        <v>11200</v>
+        <v>15100</v>
       </c>
       <c r="G61" s="3">
-        <v>9600</v>
+        <v>15600</v>
       </c>
       <c r="H61" s="3">
-        <v>9500</v>
+        <v>14200</v>
       </c>
       <c r="I61" s="3">
-        <v>9500</v>
+        <v>14400</v>
       </c>
       <c r="J61" s="3">
+        <v>14500</v>
+      </c>
+      <c r="K61" s="3">
         <v>9400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>100</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>3200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4700</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4584,68 +4727,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5100</v>
+        <v>1100</v>
       </c>
       <c r="E62" s="3">
-        <v>5400</v>
+        <v>1100</v>
       </c>
       <c r="F62" s="3">
-        <v>5600</v>
+        <v>1200</v>
       </c>
       <c r="G62" s="3">
-        <v>6600</v>
+        <v>1200</v>
       </c>
       <c r="H62" s="3">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="I62" s="3">
-        <v>6400</v>
+        <v>1300</v>
       </c>
       <c r="J62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K62" s="3">
         <v>5300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>200</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
       <c r="S62" s="3">
         <v>0</v>
       </c>
       <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>600</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4664,8 +4810,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4744,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4824,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4904,68 +5059,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E66" s="3">
         <v>55300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>48500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>52800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>51400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>37800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9300</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,8 +5142,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5014,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5094,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5174,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5228,13 +5396,13 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>175000</v>
       </c>
       <c r="V70" s="3">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -5254,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5334,68 +5505,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-592000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-561300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-521900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-486300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-440800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-389800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-355700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-325500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-294800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-259400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-226500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-202000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-173500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-149000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-132700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-118500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-99700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-89600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-78200</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5414,8 +5588,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5494,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5574,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5654,68 +5837,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>136800</v>
+      </c>
+      <c r="E76" s="3">
         <v>159300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>164200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>189700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>168800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>212700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>240400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>263500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>287000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>316300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>343600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>363000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>385200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>405000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>418500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>429800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>252000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-84400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-75900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5734,8 +5920,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5814,173 +6003,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-39400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-35600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-45500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-51000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-34200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-30200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-30700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-35300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-32900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-24500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-24600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-18800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-14000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6009,28 +6207,29 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -6045,7 +6244,7 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -6063,7 +6262,7 @@
         <v>0</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -6080,8 +6279,8 @@
       <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
+      <c r="Z83" s="3">
+        <v>100</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
@@ -6089,8 +6288,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6169,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6249,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6329,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6409,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6489,88 +6703,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-26600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-37900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-39700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-31200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-31700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-27800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-20700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-20700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-17500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-24900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-13600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6599,8 +6819,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6614,35 +6835,35 @@
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>-1300</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -6659,28 +6880,31 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6759,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6839,50 +7066,53 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E94" s="3">
         <v>900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>26500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>12800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>6200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>42300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>10900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>13700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-76100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-183900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-400</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -6890,37 +7120,40 @@
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>600</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6949,31 +7182,32 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7029,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7109,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7189,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7269,79 +7512,82 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>27200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>59200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>188400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>170300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>105000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>5900</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>9400</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
@@ -7349,31 +7595,34 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7429,84 +7678,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
         <v>1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>14400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-92700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-204500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-21500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-24800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>174700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>161400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>96000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
   <si>
     <t>ALXO</t>
   </si>
@@ -656,128 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -802,8 +805,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -833,34 +836,37 @@
         <v>0</v>
       </c>
       <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
         <v>500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1200</v>
-      </c>
-      <c r="X8" s="3">
-        <v>1300</v>
       </c>
       <c r="Y8" s="3">
         <v>1300</v>
       </c>
       <c r="Z8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA8" s="3">
         <v>1000</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -915,35 +921,38 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3">
         <v>500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>600</v>
-      </c>
-      <c r="W9" s="3">
-        <v>1100</v>
       </c>
       <c r="X9" s="3">
         <v>1100</v>
       </c>
       <c r="Y9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z9" s="3">
         <v>1200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>900</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -998,26 +1007,26 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U10" s="3">
-        <v>0</v>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3">
         <v>100</v>
       </c>
       <c r="X10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y10" s="3">
         <v>200</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>100</v>
       </c>
       <c r="Z10" s="3">
         <v>100</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
+      <c r="AA10" s="3">
+        <v>100</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
@@ -1025,8 +1034,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,91 +1068,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E12" s="3">
         <v>26500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>34700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>41800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>45800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>25200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>26700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>20900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>18200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3700</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,8 +1238,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1248,23 +1267,23 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1272,12 +1291,12 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1293,8 +1312,8 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1305,8 +1324,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1314,10 +1336,10 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
+        <v>200</v>
+      </c>
+      <c r="F15" s="3">
         <v>700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>200</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
@@ -1326,14 +1348,14 @@
         <v>200</v>
       </c>
       <c r="I15" s="3">
+        <v>200</v>
+      </c>
+      <c r="J15" s="3">
         <v>400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1388,8 +1410,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1441,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E17" s="3">
         <v>32600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>41500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>37800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>48000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>53300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>36800</v>
-      </c>
-      <c r="J17" s="3">
-        <v>32200</v>
       </c>
       <c r="K17" s="3">
         <v>32200</v>
       </c>
       <c r="L17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="M17" s="3">
         <v>36700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>33800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>28500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5300</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-32600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-41500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-37800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-48000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-53300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-36800</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-32200</v>
       </c>
       <c r="K18" s="3">
         <v>-32200</v>
       </c>
       <c r="L18" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="M18" s="3">
         <v>-36700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-33800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-28500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-16300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-18400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,8 +1645,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1634,26 +1667,26 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1667,14 +1700,14 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1687,8 +1720,8 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
+      <c r="AA20" s="3">
+        <v>0</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
@@ -1696,82 +1729,85 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-32300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-40900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-37600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-47800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-53100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-36000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-31900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-30500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-35200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-32800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-24500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-28400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-14200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-18400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-11000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-7600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-4100</v>
       </c>
       <c r="Z21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
+      <c r="AA21" s="3">
+        <v>-4100</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
@@ -1779,8 +1815,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1805,11 +1844,11 @@
       <c r="J22" s="3">
         <v>400</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3">
+        <v>400</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1830,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3">
         <v>200</v>
@@ -1842,19 +1881,19 @@
         <v>200</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
@@ -1862,82 +1901,85 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-30700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-39400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-35600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-45500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-51000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-34200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-30200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-30600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-35300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-32900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-14200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-18600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-7800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-4200</v>
       </c>
       <c r="Z23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
+      <c r="AA23" s="3">
+        <v>-4200</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
@@ -1945,8 +1987,11 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1971,20 +2016,20 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1996,11 +2041,11 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -2019,8 +2064,8 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
+      <c r="AA24" s="3">
+        <v>0</v>
       </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
@@ -2028,8 +2073,11 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,82 +2159,85 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-30700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-39400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-35600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-45500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-51000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-34200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-30200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-30700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-35300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-32900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-24500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-16300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-18800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-4200</v>
       </c>
       <c r="Z26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
+      <c r="AA26" s="3">
+        <v>-4200</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
@@ -2194,91 +2245,97 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-30700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-39400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-35600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-45500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-51000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-30200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-30700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-35300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-32900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-24500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-18800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-14000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2417,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2443,8 +2503,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2589,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,8 +2675,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2630,26 +2699,26 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2663,14 +2732,14 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2683,8 +2752,8 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
+      <c r="AA32" s="3">
+        <v>0</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
@@ -2692,91 +2761,97 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-30700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-39400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-35600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-45500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-51000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-30200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-30700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-35300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-32900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-24500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-18800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-14000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2933,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-30700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-39400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-35600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-45500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-51000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-30200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-30700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-35300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-32900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-24500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-18800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-14000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3144,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,71 +3176,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E41" s="3">
         <v>16100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>38000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>63200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>48800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>49100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>66400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>159100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>363700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>385100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>410000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>429900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>434200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>259500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>98100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>105000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,47 +3260,50 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>110200</v>
+      </c>
+      <c r="E42" s="3">
         <v>132500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>141200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>143400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>160300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>170400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>174800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>164800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>217400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>235900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>247000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>157500</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3230,8 +3319,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3257,35 +3346,38 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1100</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3295,8 +3387,8 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3311,17 +3403,17 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="U43" s="3">
         <v>500</v>
       </c>
       <c r="V43" s="3">
+        <v>500</v>
+      </c>
+      <c r="W43" s="3">
         <v>1200</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3340,8 +3432,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3366,8 +3461,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3423,25 +3518,28 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>400</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -3449,45 +3547,45 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>4800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,71 +3604,74 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>134400</v>
+      </c>
+      <c r="E46" s="3">
         <v>155900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>168700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>167900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>188700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>199100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>219600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>232500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>271000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>290800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>316800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>321500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>367000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>389000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>412300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>432300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>436000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>262400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>100700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>107400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3589,47 +3690,50 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E47" s="3">
         <v>14000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>29500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>27000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>35400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>16700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>25100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3749,8 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3672,71 +3776,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E48" s="3">
         <v>10300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7000</v>
-      </c>
-      <c r="O48" s="3">
-        <v>3400</v>
       </c>
       <c r="P48" s="3">
         <v>3400</v>
       </c>
       <c r="Q48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R48" s="3">
         <v>200</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
       <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
         <v>100</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
       <c r="V48" s="3">
+        <v>0</v>
+      </c>
+      <c r="W48" s="3">
         <v>800</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3755,8 +3862,11 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3838,8 +3948,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4034,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,71 +4120,74 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>300</v>
+      </c>
+      <c r="E52" s="3">
         <v>5500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>10100</v>
       </c>
       <c r="N52" s="3">
         <v>10100</v>
       </c>
       <c r="O52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="P52" s="3">
         <v>9800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>500</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>2400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4087,8 +4206,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,71 +4292,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>147800</v>
+      </c>
+      <c r="E54" s="3">
         <v>185700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>214600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>212700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>242600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>220100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>245900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>278100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>306500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>317700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>346000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>363700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>380200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>399700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>421300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>432900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>436100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>262400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>103100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>108400</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4253,8 +4378,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4412,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,71 +4444,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E57" s="3">
         <v>7900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7400</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4398,37 +4528,40 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1800</v>
       </c>
-      <c r="G58" s="3">
-        <v>1600</v>
-      </c>
       <c r="H58" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <v>800</v>
       </c>
       <c r="J58" s="3">
+        <v>800</v>
+      </c>
+      <c r="K58" s="3">
         <v>1000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>300</v>
-      </c>
-      <c r="L58" s="3">
-        <v>400</v>
       </c>
       <c r="M58" s="3">
         <v>400</v>
@@ -4446,23 +4579,23 @@
         <v>400</v>
       </c>
       <c r="R58" s="3">
+        <v>400</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
         <v>2600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>900</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4481,71 +4614,74 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E59" s="3">
         <v>7700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9900</v>
       </c>
-      <c r="G59" s="3">
-        <v>10400</v>
-      </c>
       <c r="H59" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I59" s="3">
         <v>12700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4564,71 +4700,74 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E60" s="3">
         <v>32300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>36000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>25200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>24000</v>
-      </c>
-      <c r="N60" s="3">
-        <v>15300</v>
       </c>
       <c r="O60" s="3">
         <v>15300</v>
       </c>
       <c r="P60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="Q60" s="3">
         <v>12500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4000</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4647,71 +4786,74 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E61" s="3">
         <v>15500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15100</v>
       </c>
-      <c r="G61" s="3">
-        <v>15600</v>
-      </c>
       <c r="H61" s="3">
+        <v>9600</v>
+      </c>
+      <c r="I61" s="3">
         <v>14200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>100</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>3200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4700</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4730,71 +4872,74 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E62" s="3">
         <v>1100</v>
       </c>
       <c r="F62" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="G62" s="3">
         <v>1200</v>
       </c>
       <c r="H62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="I62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>200</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>600</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4813,8 +4958,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5044,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5130,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,71 +5216,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E66" s="3">
         <v>48900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>55300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>48500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>52800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>51400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>37800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>29700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9300</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5145,8 +5302,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5336,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5420,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5506,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5399,13 +5566,13 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>175000</v>
       </c>
       <c r="W70" s="3">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="X70" s="3">
         <v>0</v>
@@ -5425,8 +5592,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,71 +5678,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-621100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-592000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-561300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-521900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-486300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-440800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-389800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-355700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-325500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-294800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-259400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-226500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-202000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-173500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-149000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-132700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-118500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-99700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-89600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-78200</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5591,8 +5764,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5850,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5936,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,71 +6022,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>113600</v>
+      </c>
+      <c r="E76" s="3">
         <v>136800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>159300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>164200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>189700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>168800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>212700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>240400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>263500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>287000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>316300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>343600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>363000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>385200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>405000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>418500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>429800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>252000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-84400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-75900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5923,8 +6108,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6194,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-30700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-39400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-35600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-45500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-51000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-30200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-30700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-35300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-32900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-24500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-18800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-14000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,22 +6405,23 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -6247,7 +6445,7 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -6265,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
@@ -6282,8 +6480,8 @@
       <c r="Z83" s="3">
         <v>100</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
+      <c r="AA83" s="3">
+        <v>100</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
@@ -6291,8 +6489,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6575,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6661,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6747,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6833,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,91 +6919,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-25400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-26600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-37900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-39700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-31200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-31700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-27800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-20700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-17000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-20700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-17500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-24900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-20600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-13600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-9500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,8 +7039,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6838,35 +7058,35 @@
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>1300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -6883,28 +7103,31 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7209,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,53 +7295,56 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E94" s="3">
         <v>25700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>26500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>12800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>6200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>42300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>10900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>13700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-76100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-183900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -7123,37 +7352,40 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>600</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7415,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7209,8 +7442,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7266,8 +7499,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7585,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7671,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,8 +7757,11 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7524,73 +7769,73 @@
         <v>300</v>
       </c>
       <c r="E100" s="3">
+        <v>300</v>
+      </c>
+      <c r="F100" s="3">
         <v>27200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>59200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>9500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>188400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>170300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>105000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5900</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>9400</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
+      <c r="AA100" s="3">
+        <v>0</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
@@ -7598,8 +7843,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7624,8 +7872,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7681,87 +7929,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>14400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-92700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-204500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-21500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-24800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-19900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>174700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>161400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>96000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
   <si>
     <t>ALXO</t>
   </si>
@@ -656,131 +656,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -808,8 +812,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -839,34 +843,37 @@
         <v>0</v>
       </c>
       <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>1300</v>
       </c>
       <c r="Z8" s="3">
         <v>1300</v>
       </c>
       <c r="AA8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB8" s="3">
         <v>1000</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -924,35 +931,38 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3">
         <v>500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>600</v>
-      </c>
-      <c r="X9" s="3">
-        <v>1100</v>
       </c>
       <c r="Y9" s="3">
         <v>1100</v>
       </c>
       <c r="Z9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA9" s="3">
         <v>1200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>900</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1010,26 +1020,26 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V10" s="3">
-        <v>0</v>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X10" s="3">
         <v>100</v>
       </c>
       <c r="Y10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z10" s="3">
         <v>200</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>100</v>
       </c>
       <c r="AA10" s="3">
         <v>100</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
+      <c r="AB10" s="3">
+        <v>100</v>
       </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
@@ -1037,8 +1047,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1069,94 +1082,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E12" s="3">
         <v>23500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>34700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>41800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>45800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>29500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>20900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>18200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>9800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3700</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1241,8 +1258,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1270,23 +1290,23 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
@@ -1294,12 +1314,12 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1315,8 +1335,8 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1327,8 +1347,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1339,10 +1362,10 @@
         <v>200</v>
       </c>
       <c r="F15" s="3">
+        <v>200</v>
+      </c>
+      <c r="G15" s="3">
         <v>700</v>
-      </c>
-      <c r="G15" s="3">
-        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
@@ -1351,14 +1374,14 @@
         <v>200</v>
       </c>
       <c r="J15" s="3">
+        <v>200</v>
+      </c>
+      <c r="K15" s="3">
         <v>400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1413,8 +1436,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1442,180 +1468,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E17" s="3">
         <v>30600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>32600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>41500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>37800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>48000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>53300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>36800</v>
-      </c>
-      <c r="K17" s="3">
-        <v>32200</v>
       </c>
       <c r="L17" s="3">
         <v>32200</v>
       </c>
       <c r="M17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="N17" s="3">
         <v>36700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>33800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5300</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-30600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-32600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-41500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-37800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-48000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-53300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-36800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-32200</v>
       </c>
       <c r="L18" s="3">
         <v>-32200</v>
       </c>
       <c r="M18" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="N18" s="3">
         <v>-36700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-33800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-16300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-14200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-18400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1646,8 +1679,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1670,26 +1704,26 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1703,14 +1737,14 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1757,8 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
+      <c r="AB20" s="3">
+        <v>0</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
@@ -1732,85 +1766,88 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-30400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-32300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-40900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-37600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-47800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-53100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-36000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-31900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-30500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-35200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-32800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-24500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-24600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-16300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-14200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-18400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-11000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-5100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-4100</v>
       </c>
       <c r="AA21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
+      <c r="AB21" s="3">
+        <v>-4100</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
@@ -1818,8 +1855,11 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1847,11 +1887,11 @@
       <c r="K22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3">
+        <v>400</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1872,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="U22" s="3">
         <v>200</v>
@@ -1884,19 +1924,19 @@
         <v>200</v>
       </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
@@ -1904,85 +1944,88 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-29200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-30700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-39400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-35600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-45500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-51000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-34200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-30200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-30600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-35300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-32900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-14200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-18600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-4200</v>
       </c>
       <c r="AA23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
+      <c r="AB23" s="3">
+        <v>-4200</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
@@ -1990,8 +2033,11 @@
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2019,20 +2065,20 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2044,11 +2090,11 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -2067,8 +2113,8 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
+      <c r="AB24" s="3">
+        <v>0</v>
       </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
@@ -2076,8 +2122,11 @@
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2162,85 +2211,88 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-29200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-30700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-39400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-35600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-45500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-51000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-34200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-30200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-35300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-32900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-24600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-16300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-14200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-4200</v>
       </c>
       <c r="AA26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
+      <c r="AB26" s="3">
+        <v>-4200</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
@@ -2248,94 +2300,100 @@
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-29200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-30700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-39400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-35600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-45500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-51000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-34200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-30200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-30700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-35300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-32900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-24500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-24600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-16300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-14200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-14000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2420,8 +2478,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2506,8 +2567,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2592,8 +2656,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2678,8 +2745,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2702,26 +2772,26 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2735,14 +2805,14 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2755,8 +2825,8 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
+      <c r="AB32" s="3">
+        <v>0</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
@@ -2764,94 +2834,100 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-29200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-30700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-39400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-35600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-45500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-51000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-34200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-30200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-30700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-35300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-32900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-24500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-24600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-16300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-14200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-14000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2936,185 +3012,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-29200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-30700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-39400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-35600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-45500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-51000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-34200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-30200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-30700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-35300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-32900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-24500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-24600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-16300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-14200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-14000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3145,8 +3230,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3177,74 +3263,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E41" s="3">
         <v>17600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>38000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>63200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>48800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>49100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>66400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>159100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>363700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>385100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>410000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>429900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>434200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>259500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>98100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>105000</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3263,50 +3350,53 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>77200</v>
+      </c>
+      <c r="E42" s="3">
         <v>110200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>132500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>141200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>143400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>160300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>170400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>174800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>164800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>217400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>235900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>247000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>157500</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3322,8 +3412,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3349,8 +3439,11 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3358,29 +3451,29 @@
         <v>900</v>
       </c>
       <c r="E43" s="3">
+        <v>900</v>
+      </c>
+      <c r="F43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>800</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3390,8 +3483,8 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -3406,17 +3499,17 @@
         <v>0</v>
       </c>
       <c r="U43" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3">
         <v>500</v>
       </c>
       <c r="W43" s="3">
+        <v>500</v>
+      </c>
+      <c r="X43" s="3">
         <v>1200</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3435,8 +3528,11 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3464,8 +3560,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3521,74 +3617,77 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>4800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1200</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,74 +3706,77 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E46" s="3">
         <v>134400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>155900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>168700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>167900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>188700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>199100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>219600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>232500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>271000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>290800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>316800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>321500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>367000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>389000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>412300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>432300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>436000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>262400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>100700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>107400</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3693,50 +3795,53 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E47" s="3">
         <v>3500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>29500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>27000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>35400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>16700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>25100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3752,8 +3857,8 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3779,74 +3884,77 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7000</v>
-      </c>
-      <c r="P48" s="3">
-        <v>3400</v>
       </c>
       <c r="Q48" s="3">
         <v>3400</v>
       </c>
       <c r="R48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="S48" s="3">
         <v>200</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
       <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3">
         <v>100</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
       <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3">
         <v>800</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3973,11 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3951,8 +4062,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4037,8 +4151,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4123,8 +4240,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4132,65 +4252,65 @@
         <v>300</v>
       </c>
       <c r="E52" s="3">
+        <v>300</v>
+      </c>
+      <c r="F52" s="3">
         <v>5500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10000</v>
-      </c>
-      <c r="N52" s="3">
-        <v>10100</v>
       </c>
       <c r="O52" s="3">
         <v>10100</v>
       </c>
       <c r="P52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>9800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>500</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
       <c r="U52" s="3">
         <v>0</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>2400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,8 +4329,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4295,74 +4418,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>120900</v>
+      </c>
+      <c r="E54" s="3">
         <v>147800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>185700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>214600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>212700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>242600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>220100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>245900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>278100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>306500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>317700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>346000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>363700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>380200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>399700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>421300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>432900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>436100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>262400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>103100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>108400</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4381,8 +4507,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4413,8 +4542,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4445,74 +4575,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>4500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7400</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
       <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
         <v>1400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2000</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,40 +4662,43 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1800</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>800</v>
       </c>
       <c r="K58" s="3">
+        <v>800</v>
+      </c>
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
-      </c>
-      <c r="M58" s="3">
-        <v>400</v>
       </c>
       <c r="N58" s="3">
         <v>400</v>
@@ -4582,23 +4716,23 @@
         <v>400</v>
       </c>
       <c r="S58" s="3">
+        <v>400</v>
+      </c>
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3">
         <v>2600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>900</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4617,74 +4751,77 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,74 +4840,77 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E60" s="3">
         <v>18500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>36000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>25200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>24000</v>
-      </c>
-      <c r="O60" s="3">
-        <v>15300</v>
       </c>
       <c r="P60" s="3">
         <v>15300</v>
       </c>
       <c r="Q60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="R60" s="3">
         <v>12500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4000</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,74 +4929,77 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E61" s="3">
         <v>14600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9400</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>100</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>3200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4700</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4875,8 +5018,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4884,65 +5030,65 @@
         <v>1000</v>
       </c>
       <c r="E62" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F62" s="3">
         <v>1100</v>
       </c>
       <c r="G62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H62" s="3">
         <v>1200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>200</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
       <c r="U62" s="3">
         <v>0</v>
       </c>
       <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
         <v>800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>600</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4961,8 +5107,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5047,8 +5196,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5133,8 +5285,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5219,74 +5374,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E66" s="3">
         <v>34200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>48900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>52800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>51400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>43000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9300</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5305,8 +5463,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5337,8 +5498,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5423,8 +5585,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5509,8 +5674,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5569,13 +5737,13 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>175000</v>
       </c>
       <c r="X70" s="3">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
@@ -5595,8 +5763,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5681,74 +5852,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-651900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-621100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-592000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-561300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-521900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-486300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-440800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-389800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-355700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-325500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-294800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-259400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-226500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-202000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-173500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-149000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-132700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-118500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-99700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-89600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-78200</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5767,8 +5941,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5853,8 +6030,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5939,8 +6119,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6025,74 +6208,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>88300</v>
+      </c>
+      <c r="E76" s="3">
         <v>113600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>136800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>159300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>164200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>189700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>168800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>212700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>240400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>263500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>287000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>316300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>343600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>363000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>385200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>405000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>418500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>429800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>252000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-84400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-75900</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6111,8 +6297,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6197,185 +6386,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-29200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-30700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-39400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-35600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-45500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-51000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-34200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-30200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-30700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-35300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-32900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-24500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-24600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-16300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-14200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-14000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6406,8 +6604,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6415,16 +6614,16 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
-      </c>
-      <c r="H83" s="3">
-        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -6448,7 +6647,7 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -6466,7 +6665,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
@@ -6483,8 +6682,8 @@
       <c r="AA83" s="3">
         <v>100</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
+      <c r="AB83" s="3">
+        <v>100</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
@@ -6492,8 +6691,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6578,8 +6780,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6664,8 +6869,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6750,8 +6958,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6836,8 +7047,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6922,94 +7136,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-25400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-26600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-37900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-39700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-31200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-31700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-27800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-20700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-30900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-17000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-20700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-24900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-20600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-13600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-9000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7040,8 +7260,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7061,35 +7282,35 @@
         <v>-100</v>
       </c>
       <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>1300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -7106,28 +7327,31 @@
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7212,8 +7436,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7298,56 +7525,59 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E94" s="3">
         <v>33200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>25700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>26500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>12800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>6200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>42300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>10900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>13700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-76100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-183900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -7355,37 +7585,40 @@
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>600</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>100</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7416,8 +7649,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7445,8 +7679,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7502,8 +7736,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7588,8 +7825,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7674,8 +7914,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7760,85 +8003,88 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
         <v>300</v>
       </c>
       <c r="F100" s="3">
+        <v>300</v>
+      </c>
+      <c r="G100" s="3">
         <v>27200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>59200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>9500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>188400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>170300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>105000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5900</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>9400</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
+      <c r="AB100" s="3">
+        <v>0</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
@@ -7846,8 +8092,11 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7875,8 +8124,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7932,90 +8181,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>14400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-92700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-204500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-24800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-19900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>174700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>161400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>96000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
   <si>
     <t>ALXO</t>
   </si>
@@ -656,135 +656,139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -815,8 +819,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -846,34 +850,37 @@
         <v>0</v>
       </c>
       <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>1300</v>
       </c>
       <c r="AA8" s="3">
         <v>1300</v>
       </c>
       <c r="AB8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AC8" s="3">
         <v>1000</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -934,35 +941,38 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3">
         <v>500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>600</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>1100</v>
       </c>
       <c r="Z9" s="3">
         <v>1100</v>
       </c>
       <c r="AA9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB9" s="3">
         <v>1200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>900</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1023,26 +1033,26 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W10" s="3">
-        <v>0</v>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3">
         <v>100</v>
       </c>
       <c r="Z10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA10" s="3">
         <v>200</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>100</v>
       </c>
       <c r="AB10" s="3">
         <v>100</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
+      <c r="AC10" s="3">
+        <v>100</v>
       </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
@@ -1050,8 +1060,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1083,97 +1096,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E12" s="3">
         <v>23900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>34700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>31700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>41800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>45800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>18200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>11200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3700</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,13 +1278,16 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>3200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1293,23 +1313,23 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
@@ -1317,12 +1337,12 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
         <v>600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1338,8 +1358,8 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1350,8 +1370,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1365,7 +1388,7 @@
         <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
@@ -1377,14 +1400,14 @@
         <v>200</v>
       </c>
       <c r="K15" s="3">
+        <v>200</v>
+      </c>
+      <c r="L15" s="3">
         <v>400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1439,8 +1462,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1469,186 +1495,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E17" s="3">
         <v>31800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>30600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>32600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>41500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>37800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>48000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>53300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36800</v>
-      </c>
-      <c r="L17" s="3">
-        <v>32200</v>
       </c>
       <c r="M17" s="3">
         <v>32200</v>
       </c>
       <c r="N17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="O17" s="3">
         <v>36700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>33800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>24600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5300</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-31800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-30600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-32600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-41500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-37800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-48000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-53300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-36800</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-32200</v>
       </c>
       <c r="M18" s="3">
         <v>-32200</v>
       </c>
       <c r="N18" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="O18" s="3">
         <v>-36700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-33800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-28500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-24600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-16300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-14200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-18400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1680,8 +1713,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1707,26 +1741,26 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1740,14 +1774,14 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1760,8 +1794,8 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
+      <c r="AC20" s="3">
+        <v>0</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
@@ -1769,88 +1803,91 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-31600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-30400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-32300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-40900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-37600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-47800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-53100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-36000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-31900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-30500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-35200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-32800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-28400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-24600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-16300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-14200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-18400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-11000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-4100</v>
       </c>
       <c r="AB21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
+      <c r="AC21" s="3">
+        <v>-4100</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
@@ -1858,8 +1895,11 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1890,11 +1930,11 @@
       <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3">
+        <v>400</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1915,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3">
         <v>200</v>
@@ -1927,19 +1967,19 @@
         <v>200</v>
       </c>
       <c r="Y22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
@@ -1947,88 +1987,91 @@
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-30800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-29200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-30700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-39400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-35600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-45500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-51000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-34200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-30200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-30600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-35300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-32900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-28500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-24600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-14200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-18600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3000</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-4200</v>
       </c>
       <c r="AB23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
+      <c r="AC23" s="3">
+        <v>-4200</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
@@ -2036,8 +2079,11 @@
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2068,20 +2114,20 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2093,11 +2139,11 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
@@ -2116,8 +2162,8 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
+      <c r="AC24" s="3">
+        <v>0</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
@@ -2125,8 +2171,11 @@
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2214,88 +2263,91 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-30800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-29200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-30700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-39400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-35600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-45500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-51000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-34200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-30700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-35300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-32900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-28400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-24600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-16300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-14200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-18800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3000</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-4200</v>
       </c>
       <c r="AB26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
+      <c r="AC26" s="3">
+        <v>-4200</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
@@ -2303,97 +2355,103 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-30800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-29200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-30700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-39400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-35600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-45500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-51000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-34200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-30200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-30700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-35300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-32900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-28400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-24600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-16300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-14200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-18800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-14000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2481,8 +2539,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2570,8 +2631,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2659,8 +2723,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2748,8 +2815,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2775,26 +2845,26 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2808,14 +2878,14 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>300</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2828,8 +2898,8 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
+      <c r="AC32" s="3">
+        <v>0</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
@@ -2837,97 +2907,103 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-30800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-29200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-30700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-39400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-35600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-45500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-51000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-34200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-30200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-30700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-35300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-32900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-28400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-24600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-16300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-14200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-18800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-14000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3015,191 +3091,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-30800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-29200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-30700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-39400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-35600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-45500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-51000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-34200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-30200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-30700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-35300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-32900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-28400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-24600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-16300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-14200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-18800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-14000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3231,8 +3316,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3264,77 +3350,78 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E41" s="3">
         <v>20600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>38000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>63200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>48800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>49100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>66400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>159100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>363700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>385100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>410000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>429900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>434200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>259500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>98100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>105000</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,53 +3440,56 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E42" s="3">
         <v>77200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>110200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>132500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>141200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>143400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>160300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>170400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>174800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>164800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>217400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>235900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>247000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>157500</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3415,8 +3505,8 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3442,41 +3532,44 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="E43" s="3">
         <v>900</v>
       </c>
       <c r="F43" s="3">
+        <v>900</v>
+      </c>
+      <c r="G43" s="3">
         <v>1200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>800</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3486,8 +3579,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -3502,17 +3595,17 @@
         <v>0</v>
       </c>
       <c r="V43" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W43" s="3">
         <v>500</v>
       </c>
       <c r="X43" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y43" s="3">
         <v>1200</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3531,8 +3624,11 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3563,8 +3659,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3620,77 +3716,80 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>4800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1200</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3709,77 +3808,80 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>85300</v>
+      </c>
+      <c r="E46" s="3">
         <v>102500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>134400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>155900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>168700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>167900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>188700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>199100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>219600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>232500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>271000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>290800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>316800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>321500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>367000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>389000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>412300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>432300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>436000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>262400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>100700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>107400</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3798,53 +3900,56 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E47" s="3">
         <v>9200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>14000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>29500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>27000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>35400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>16700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>25100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3860,8 +3965,8 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3887,77 +3992,80 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E48" s="3">
         <v>9000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7000</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>3400</v>
       </c>
       <c r="R48" s="3">
         <v>3400</v>
       </c>
       <c r="S48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="T48" s="3">
         <v>200</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
       <c r="U48" s="3">
+        <v>0</v>
+      </c>
+      <c r="V48" s="3">
         <v>100</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
       <c r="W48" s="3">
         <v>0</v>
       </c>
       <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
         <v>800</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3976,8 +4084,11 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4065,8 +4176,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4154,8 +4268,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4243,77 +4360,80 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="E52" s="3">
         <v>300</v>
       </c>
       <c r="F52" s="3">
+        <v>300</v>
+      </c>
+      <c r="G52" s="3">
         <v>5500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10000</v>
-      </c>
-      <c r="O52" s="3">
-        <v>10100</v>
       </c>
       <c r="P52" s="3">
         <v>10100</v>
       </c>
       <c r="Q52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="R52" s="3">
         <v>9800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>500</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
       <c r="V52" s="3">
         <v>0</v>
       </c>
       <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
         <v>2400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>200</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4332,8 +4452,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4421,77 +4544,80 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E54" s="3">
         <v>120900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>147800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>185700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>214600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>212700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>242600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>220100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>245900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>278100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>306500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>317700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>346000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>363700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>380200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>399700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>421300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>432900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>436100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>262400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>103100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>108400</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4510,8 +4636,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4543,8 +4672,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4576,77 +4706,78 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7400</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
       <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
         <v>1400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2000</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,43 +4796,46 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E58" s="3">
         <v>3700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1800</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>800</v>
       </c>
       <c r="L58" s="3">
+        <v>800</v>
+      </c>
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>300</v>
-      </c>
-      <c r="N58" s="3">
-        <v>400</v>
       </c>
       <c r="O58" s="3">
         <v>400</v>
@@ -4719,23 +4853,23 @@
         <v>400</v>
       </c>
       <c r="T58" s="3">
+        <v>400</v>
+      </c>
+      <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
         <v>2600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>900</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4754,77 +4888,80 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1100</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4843,77 +4980,80 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E60" s="3">
         <v>18700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>38400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>36000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>25200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>24000</v>
-      </c>
-      <c r="P60" s="3">
-        <v>15300</v>
       </c>
       <c r="Q60" s="3">
         <v>15300</v>
       </c>
       <c r="R60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="S60" s="3">
         <v>12500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4000</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,77 +5072,80 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E61" s="3">
         <v>12900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9400</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>100</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>3200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4700</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5021,77 +5164,80 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E62" s="3">
         <v>1000</v>
       </c>
       <c r="F62" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G62" s="3">
         <v>1100</v>
       </c>
       <c r="H62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I62" s="3">
         <v>1200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>200</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
       <c r="V62" s="3">
         <v>0</v>
       </c>
       <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
         <v>800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>600</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5110,8 +5256,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5199,8 +5348,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5288,8 +5440,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5377,77 +5532,80 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E66" s="3">
         <v>32600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>34200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>48900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>55300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>51400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>43000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9300</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5466,8 +5624,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5499,8 +5660,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5588,8 +5750,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5677,8 +5842,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5740,13 +5908,13 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="X70" s="3">
         <v>175000</v>
       </c>
       <c r="Y70" s="3">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="Z70" s="3">
         <v>0</v>
@@ -5766,8 +5934,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5855,77 +6026,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-677800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-651900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-621100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-592000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-561300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-521900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-486300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-440800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-389800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-355700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-325500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-294800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-259400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-226500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-202000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-173500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-149000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-132700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-118500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-99700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-89600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-78200</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5944,8 +6118,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6033,8 +6210,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6122,8 +6302,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6211,77 +6394,80 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E76" s="3">
         <v>88300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>113600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>136800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>159300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>164200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>189700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>168800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>212700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>240400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>263500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>287000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>316300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>343600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>363000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>385200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>405000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>418500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>429800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>252000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-84400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-75900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6300,8 +6486,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6389,191 +6578,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-30800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-29200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-30700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-39400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-35600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-45500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-51000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-34200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-30200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-30700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-35300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-32900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-28400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-24600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-16300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-14200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-18800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-14000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6605,8 +6803,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6617,16 +6816,16 @@
         <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -6650,7 +6849,7 @@
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -6668,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X83" s="3">
         <v>100</v>
@@ -6685,8 +6884,8 @@
       <c r="AB83" s="3">
         <v>100</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
+      <c r="AC83" s="3">
+        <v>100</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
@@ -6694,8 +6893,11 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6783,8 +6985,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6872,8 +7077,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6961,8 +7169,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7050,8 +7261,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7139,97 +7353,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-24700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-32000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-25400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-26600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-37900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-39700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-31200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-31700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-27800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-20700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-30900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-17000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-17500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-24900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-20600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-13600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7261,13 +7481,14 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
@@ -7285,35 +7506,35 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
         <v>1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -7330,28 +7551,31 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>100</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7439,8 +7663,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7528,59 +7755,62 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E94" s="3">
         <v>27600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>33200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>25700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>26500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>12800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>6200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>42300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>10900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>13700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-76100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-183900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -7588,37 +7818,40 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>600</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>100</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7650,8 +7883,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7682,8 +7916,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7739,8 +7973,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7828,8 +8065,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7917,8 +8157,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8006,88 +8249,91 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
-      </c>
-      <c r="E100" s="3">
-        <v>300</v>
       </c>
       <c r="F100" s="3">
         <v>300</v>
       </c>
       <c r="G100" s="3">
+        <v>300</v>
+      </c>
+      <c r="H100" s="3">
         <v>27200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>59200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>188400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>170300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>105000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>5900</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>9400</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
+      <c r="AC100" s="3">
+        <v>0</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
@@ -8095,8 +8341,11 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8127,8 +8376,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8184,93 +8433,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E102" s="3">
         <v>3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-25200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>14400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-92700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-204500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-21500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-24800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-19900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>174700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>161400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>96000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
   <si>
     <t>ALXO</t>
   </si>
@@ -656,143 +656,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -829,8 +832,8 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -860,34 +863,37 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
         <v>500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1200</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>1300</v>
       </c>
       <c r="AC8" s="3">
         <v>1300</v>
       </c>
       <c r="AD8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AE8" s="3">
         <v>1000</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -954,35 +960,38 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="3">
         <v>500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>600</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>1100</v>
       </c>
       <c r="AB9" s="3">
         <v>1100</v>
       </c>
       <c r="AC9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD9" s="3">
         <v>1200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>900</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1049,26 +1058,26 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y10" s="3">
-        <v>0</v>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="3">
         <v>100</v>
       </c>
       <c r="AB10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC10" s="3">
         <v>200</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>100</v>
       </c>
       <c r="AD10" s="3">
         <v>100</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
+      <c r="AE10" s="3">
+        <v>100</v>
       </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
@@ -1076,8 +1085,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,103 +1123,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E12" s="3">
         <v>17400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>34700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>31700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>41800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>45800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>29400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>26700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>20900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>18200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>11200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>6700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3700</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,20 +1317,23 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>3200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1339,23 +1358,23 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
@@ -1363,12 +1382,12 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
         <v>600</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1403,8 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1396,8 +1415,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1429,14 +1451,14 @@
         <v>200</v>
       </c>
       <c r="M15" s="3">
+        <v>200</v>
+      </c>
+      <c r="N15" s="3">
         <v>400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1491,8 +1513,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1548,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E17" s="3">
         <v>22500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>31800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>30600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>32600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>37800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>48000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>53300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36800</v>
-      </c>
-      <c r="N17" s="3">
-        <v>32200</v>
       </c>
       <c r="O17" s="3">
         <v>32200</v>
       </c>
       <c r="P17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="Q17" s="3">
         <v>36700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>33800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>24700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5300</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-22500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-23500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-31800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-30600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-32600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-41500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-37800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-48000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-53300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-36800</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-32200</v>
       </c>
       <c r="O18" s="3">
         <v>-32200</v>
       </c>
       <c r="P18" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-36700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-33800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-24700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-28500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-24600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-16300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-14200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-18400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,8 +1780,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1781,26 +1814,26 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1814,14 +1847,14 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-300</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1834,8 +1867,8 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
+      <c r="AE20" s="3">
+        <v>0</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
@@ -1843,94 +1876,97 @@
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-22400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-23300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-31600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-30400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-32300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-41300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-37600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-47800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-53100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-36000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-31900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-30500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-35200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-32800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-24500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-28400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-24600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-16300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-14200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-18400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>-4100</v>
       </c>
       <c r="AD21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
+      <c r="AE21" s="3">
+        <v>-4100</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
@@ -1938,8 +1974,11 @@
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1976,11 +2015,11 @@
       <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3">
+        <v>400</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2001,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X22" s="3">
         <v>200</v>
@@ -2013,19 +2052,19 @@
         <v>200</v>
       </c>
       <c r="AA22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>3</v>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>3</v>
@@ -2033,94 +2072,97 @@
       <c r="AG22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-22100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-30800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-29200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-30700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-39400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-35600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-45500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-51000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-34200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-30200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-30600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-32900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-24500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-28500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-24600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-16300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-14200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-18600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3000</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-4200</v>
       </c>
       <c r="AD23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
+      <c r="AE23" s="3">
+        <v>-4200</v>
       </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
@@ -2128,8 +2170,11 @@
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2166,20 +2211,20 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -2191,11 +2236,11 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
@@ -2214,8 +2259,8 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
+      <c r="AE24" s="3">
+        <v>0</v>
       </c>
       <c r="AF24" s="3" t="s">
         <v>3</v>
@@ -2223,8 +2268,11 @@
       <c r="AG24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,94 +2366,97 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-22100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-30800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-29200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-30700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-39400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-35600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-45500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-51000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-34200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-30200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-30700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-32900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-24500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-28400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-24600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-16300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-14200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-18800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3000</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-4200</v>
       </c>
       <c r="AD26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
+      <c r="AE26" s="3">
+        <v>-4200</v>
       </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
@@ -2413,103 +2464,109 @@
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-22100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-30800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-29200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-30700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-39400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-35600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-45500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-51000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-34200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-30200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-30700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-32900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-24500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-28400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-24600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-16300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-14200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-18800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2660,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2758,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2856,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,8 +2954,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2921,26 +2990,26 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2954,14 +3023,14 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>300</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -2974,8 +3043,8 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
+      <c r="AE32" s="3">
+        <v>0</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
@@ -2983,103 +3052,109 @@
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-22100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-30800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-29200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-30700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-39400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-35600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-45500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-51000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-34200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-30200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-30700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-32900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-24500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-28400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-24600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-16300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-14200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-18800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3248,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-22100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-30800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-29200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-30700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-39400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-35600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-45500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-51000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-34200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-30200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-30700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-32900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-24500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-28400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-24600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-16300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-14200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-18800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3487,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,83 +3523,84 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E41" s="3">
         <v>23400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>22400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>38000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>63200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>48800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>49100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>66400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>159100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>363700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>385100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>410000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>429900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>434200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>259500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>98100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>105000</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,59 +3619,62 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E42" s="3">
         <v>37200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>60000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>77200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>110200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>132500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>141200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>143400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>160300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>170400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>174800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>164800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>217400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>235900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>247000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>157500</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3601,8 +3690,8 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3628,47 +3717,50 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>700</v>
-      </c>
-      <c r="F43" s="3">
-        <v>900</v>
       </c>
       <c r="G43" s="3">
         <v>900</v>
       </c>
       <c r="H43" s="3">
+        <v>900</v>
+      </c>
+      <c r="I43" s="3">
         <v>1200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3678,8 +3770,8 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3694,17 +3786,17 @@
         <v>0</v>
       </c>
       <c r="X43" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="3">
         <v>500</v>
       </c>
       <c r="Z43" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA43" s="3">
         <v>1200</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,8 +3815,11 @@
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3761,8 +3856,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3818,83 +3913,86 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>4800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1200</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3913,83 +4011,86 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E46" s="3">
         <v>66500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>85300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>102500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>134400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>155900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>168700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>167900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>188700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>199100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>219600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>232500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>271000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>290800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>316800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>321500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>367000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>389000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>412300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>432300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>436000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>262400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>100700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>107400</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4008,59 +4109,62 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E47" s="3">
         <v>5800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>29500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>27000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>35400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>28200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>16700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>25100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4076,8 +4180,8 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -4103,83 +4207,86 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7000</v>
-      </c>
-      <c r="S48" s="3">
-        <v>3400</v>
       </c>
       <c r="T48" s="3">
         <v>3400</v>
       </c>
       <c r="U48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="V48" s="3">
         <v>200</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
       <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3">
         <v>100</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
-      </c>
       <c r="Y48" s="3">
         <v>0</v>
       </c>
       <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="3">
         <v>800</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,8 +4305,11 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4293,8 +4403,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4501,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,83 +4599,86 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>700</v>
-      </c>
-      <c r="F52" s="3">
-        <v>300</v>
       </c>
       <c r="G52" s="3">
         <v>300</v>
       </c>
       <c r="H52" s="3">
+        <v>300</v>
+      </c>
+      <c r="I52" s="3">
         <v>5500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10000</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>10100</v>
       </c>
       <c r="R52" s="3">
         <v>10100</v>
       </c>
       <c r="S52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="T52" s="3">
         <v>9800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>500</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
       <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
         <v>2400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>200</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4578,8 +4697,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,83 +4795,86 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E54" s="3">
         <v>82700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>95300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>120900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>147800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>185700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>214600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>212700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>242600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>220100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>245900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>278100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>306500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>317700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>346000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>363700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>380200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>399700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>421300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>432900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>436100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>262400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>103100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>108400</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4768,8 +4893,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4931,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,83 +4967,84 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
         <v>6600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7400</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
       <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
         <v>1400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2000</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4933,49 +5063,52 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E58" s="3">
         <v>6300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3700</v>
       </c>
-      <c r="G58" s="3">
-        <v>2300</v>
-      </c>
       <c r="H58" s="3">
+        <v>400</v>
+      </c>
+      <c r="I58" s="3">
         <v>1900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>800</v>
       </c>
       <c r="N58" s="3">
+        <v>800</v>
+      </c>
+      <c r="O58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>300</v>
-      </c>
-      <c r="P58" s="3">
-        <v>400</v>
       </c>
       <c r="Q58" s="3">
         <v>400</v>
@@ -4993,23 +5126,23 @@
         <v>400</v>
       </c>
       <c r="V58" s="3">
+        <v>400</v>
+      </c>
+      <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3">
         <v>2600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>900</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5028,83 +5161,86 @@
       <c r="AG58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1800</v>
       </c>
-      <c r="G59" s="3">
-        <v>2400</v>
-      </c>
       <c r="H59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I59" s="3">
         <v>7700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5123,83 +5259,86 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E60" s="3">
         <v>27700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>38400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>36000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>35100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24000</v>
-      </c>
-      <c r="R60" s="3">
-        <v>15300</v>
       </c>
       <c r="S60" s="3">
         <v>15300</v>
       </c>
       <c r="T60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="U60" s="3">
         <v>12500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4000</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5218,83 +5357,86 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E61" s="3">
         <v>9300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12900</v>
       </c>
-      <c r="G61" s="3">
-        <v>14600</v>
-      </c>
       <c r="H61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="I61" s="3">
         <v>15500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9400</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>100</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>3200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4700</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5313,83 +5455,86 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E62" s="3">
         <v>900</v>
       </c>
       <c r="F62" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="G62" s="3">
         <v>1000</v>
       </c>
       <c r="H62" s="3">
-        <v>1100</v>
+        <v>6200</v>
       </c>
       <c r="I62" s="3">
         <v>1100</v>
       </c>
       <c r="J62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K62" s="3">
         <v>1200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>200</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
       <c r="X62" s="3">
         <v>0</v>
       </c>
       <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
         <v>800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>600</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5408,8 +5553,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5651,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5749,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,83 +5847,86 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E66" s="3">
         <v>37900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>30900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>55300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>48500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>51400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>43000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>30700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>12500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9300</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5788,8 +5945,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5983,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6079,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6177,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6082,13 +6249,13 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3">
         <v>175000</v>
       </c>
       <c r="AA70" s="3">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="AB70" s="3">
         <v>0</v>
@@ -6108,8 +6275,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,83 +6373,86 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-722800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-700000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-677800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-651900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-621100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-592000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-561300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-521900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-486300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-440800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-389800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-355700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-325500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-294800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-259400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-226500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-202000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-173500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-149000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-132700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-118500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-99700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-89600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-78200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6298,8 +6471,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6569,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6667,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,83 +6765,86 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E76" s="3">
         <v>44800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>64400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>88300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>113600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>136800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>159300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>164200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>189700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>168800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>212700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>240400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>263500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>287000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>316300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>343600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>363000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>385200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>405000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>418500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>429800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>252000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-84400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-75900</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6678,8 +6863,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6961,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-22100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-30800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-29200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-30700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-39400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-35600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-45500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-51000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-34200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-30200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-30700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-32900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-24500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-28400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-24600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-16300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-14200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-18800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7200,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7030,7 +7228,7 @@
         <v>200</v>
       </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
@@ -7054,7 +7252,7 @@
         <v>100</v>
       </c>
       <c r="S83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -7072,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="Y83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z83" s="3">
         <v>100</v>
@@ -7089,8 +7287,8 @@
       <c r="AD83" s="3">
         <v>100</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
+      <c r="AE83" s="3">
+        <v>100</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
@@ -7098,8 +7296,11 @@
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7394,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7492,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7590,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7688,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7786,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-17100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-23400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-24700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-32000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-25400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-26600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-37900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-39700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-31200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-31700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-27800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-20700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-17000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-20700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-17500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-24900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-20600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-13600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,19 +7922,20 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
@@ -7733,35 +7953,35 @@
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>1300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -7778,28 +7998,31 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>100</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8116,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,65 +8214,68 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E94" s="3">
         <v>21400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>22300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>27600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>33200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>25700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>26500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>12800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>6200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>42300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>10900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>13700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-76100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-183900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
@@ -8054,37 +8283,40 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>600</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8350,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8156,8 +8389,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8213,8 +8446,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8544,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8642,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,94 +8740,97 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-200</v>
+        <v>700</v>
       </c>
       <c r="E100" s="3">
         <v>-200</v>
       </c>
       <c r="F100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
-      </c>
-      <c r="G100" s="3">
-        <v>300</v>
       </c>
       <c r="H100" s="3">
         <v>300</v>
       </c>
       <c r="I100" s="3">
+        <v>300</v>
+      </c>
+      <c r="J100" s="3">
         <v>27200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>59200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>9500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>188400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>170300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>105000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>5900</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>9400</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
+      <c r="AE100" s="3">
+        <v>0</v>
       </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
@@ -8593,8 +8838,11 @@
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8631,8 +8879,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8688,99 +8936,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E102" s="3">
         <v>4100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-25200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>14400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-92700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-204500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-21500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-24800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-19900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>174700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>161400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>96000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>4800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALXO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="92">
   <si>
     <t>ALXO</t>
   </si>
@@ -656,146 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -835,8 +839,8 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -866,34 +870,37 @@
         <v>0</v>
       </c>
       <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
         <v>500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>1300</v>
       </c>
       <c r="AD8" s="3">
         <v>1300</v>
       </c>
       <c r="AE8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AF8" s="3">
         <v>1000</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -963,35 +970,38 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA9" s="3">
         <v>500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>600</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>1100</v>
       </c>
       <c r="AC9" s="3">
         <v>1100</v>
       </c>
       <c r="AD9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE9" s="3">
         <v>1200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>900</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1061,26 +1071,26 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z10" s="3">
-        <v>0</v>
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="3">
         <v>100</v>
       </c>
       <c r="AC10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD10" s="3">
         <v>200</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>100</v>
       </c>
       <c r="AE10" s="3">
         <v>100</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>3</v>
+      <c r="AF10" s="3">
+        <v>100</v>
       </c>
       <c r="AG10" s="3" t="s">
         <v>3</v>
@@ -1088,8 +1098,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1124,106 +1137,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E12" s="3">
         <v>17600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>34700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>31700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>41800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>45800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>29400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>26700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>17100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>18200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>11200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>5300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>6700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3700</v>
       </c>
-      <c r="AF12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1320,23 +1337,26 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>3200</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1361,23 +1381,23 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
@@ -1385,12 +1405,12 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
         <v>600</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1406,8 +1426,8 @@
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1418,8 +1438,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1454,14 +1477,14 @@
         <v>200</v>
       </c>
       <c r="N15" s="3">
+        <v>200</v>
+      </c>
+      <c r="O15" s="3">
         <v>400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1516,8 +1539,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1549,204 +1575,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E17" s="3">
         <v>23000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>31800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>30600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>32600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>48000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>53300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36800</v>
-      </c>
-      <c r="O17" s="3">
-        <v>32200</v>
       </c>
       <c r="P17" s="3">
         <v>32200</v>
       </c>
       <c r="Q17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="R17" s="3">
         <v>36700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>33800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>24700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>28500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>24600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>11300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5300</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-23000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-22500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-23500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-31800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-30600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-32600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-41500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-37800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-48000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-53300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-36800</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-32200</v>
       </c>
       <c r="P18" s="3">
         <v>-32200</v>
       </c>
       <c r="Q18" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="R18" s="3">
         <v>-36700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-33800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-24700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-28500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-24600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-16300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-14200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1781,13 +1814,14 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1817,26 +1851,26 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1850,14 +1884,14 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-300</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1870,8 +1904,8 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
+      <c r="AF20" s="3">
+        <v>0</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
@@ -1879,97 +1913,100 @@
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-22900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-22400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-23300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-31600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-30400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-32300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-41300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-37600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-47800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-53100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-36000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-31900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-35200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-32800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-24500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-28400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-24600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-16300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-14200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-7600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>-4100</v>
       </c>
       <c r="AE21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
+      <c r="AF21" s="3">
+        <v>-4100</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
@@ -1977,13 +2014,16 @@
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E22" s="3">
         <v>400</v>
@@ -2018,11 +2058,11 @@
       <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2043,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="3">
         <v>200</v>
@@ -2055,19 +2095,19 @@
         <v>200</v>
       </c>
       <c r="AB22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="3" t="s">
-        <v>3</v>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
       </c>
       <c r="AG22" s="3" t="s">
         <v>3</v>
@@ -2075,97 +2115,100 @@
       <c r="AH22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-22800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-22100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-30800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-29200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-30700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-39400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-35600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-45500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-51000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-34200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-30200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-35300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-32900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-24500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-28500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-24600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-16300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-14200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-18600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3000</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-4200</v>
       </c>
       <c r="AE23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
+      <c r="AF23" s="3">
+        <v>-4200</v>
       </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
@@ -2173,8 +2216,11 @@
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2214,20 +2260,20 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -2239,11 +2285,11 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
@@ -2262,8 +2308,8 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
+      <c r="AF24" s="3">
+        <v>0</v>
       </c>
       <c r="AG24" s="3" t="s">
         <v>3</v>
@@ -2271,8 +2317,11 @@
       <c r="AH24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2369,97 +2418,100 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-22800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-22100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-30800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-29200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-30700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-39400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-35600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-45500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-51000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-34200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-30200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-35300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-32900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-24500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-28400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-24600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-16300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-14200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3000</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-4200</v>
       </c>
       <c r="AE26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
+      <c r="AF26" s="3">
+        <v>-4200</v>
       </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
@@ -2467,106 +2519,112 @@
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-22800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-22100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-30800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-29200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-30700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-39400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-35600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-45500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-51000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-34200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-30200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-35300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-32900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-24500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-28400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-24600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-16300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-14200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2663,8 +2721,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2761,8 +2822,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2859,8 +2923,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2957,13 +3024,16 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2993,26 +3063,26 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3026,14 +3096,14 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>300</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -3046,8 +3116,8 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
+      <c r="AF32" s="3">
+        <v>0</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
@@ -3055,106 +3125,112 @@
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-22800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-22100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-30800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-29200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-30700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-39400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-35600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-45500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-51000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-34200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-30200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-35300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-32900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-24500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-28400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-24600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-16300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-14200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3251,209 +3327,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-22800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-22100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-30800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-29200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-30700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-39400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-35600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-45500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-51000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-34200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-30200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-35300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-32900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-24500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-28400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-24600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-16300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-14200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3488,8 +3573,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3524,86 +3610,87 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E41" s="3">
         <v>16400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>38000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>63200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>48800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>49100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>66400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>159100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>363700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>385100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>410000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>429900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>434200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>259500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>98100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>105000</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,62 +3709,65 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E42" s="3">
         <v>28400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>37200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>60000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>77200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>110200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>132500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>141200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>143400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>160300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>170400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>174800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>164800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>217400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>235900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>247000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>157500</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3693,8 +3783,8 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3720,50 +3810,53 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
-      </c>
-      <c r="G43" s="3">
-        <v>900</v>
       </c>
       <c r="H43" s="3">
         <v>900</v>
       </c>
       <c r="I43" s="3">
+        <v>900</v>
+      </c>
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>800</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3773,8 +3866,8 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -3789,17 +3882,17 @@
         <v>0</v>
       </c>
       <c r="Y43" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3">
         <v>500</v>
       </c>
       <c r="AA43" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB43" s="3">
         <v>1200</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3818,8 +3911,11 @@
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3859,8 +3955,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3916,86 +4012,89 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>4800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1200</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4014,86 +4113,89 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>145600</v>
+      </c>
+      <c r="E46" s="3">
         <v>50700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>66500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>85300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>102500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>134400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>155900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>168700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>167900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>188700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>199100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>219600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>232500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>271000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>290800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>316800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>321500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>367000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>389000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>412300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>432300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>436000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>262400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>100700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>107400</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4112,62 +4214,65 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E47" s="3">
         <v>3500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>27000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>35400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>28200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>16700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>10900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>25100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4183,8 +4288,8 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -4210,86 +4315,89 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7000</v>
-      </c>
-      <c r="T48" s="3">
-        <v>3400</v>
       </c>
       <c r="U48" s="3">
         <v>3400</v>
       </c>
       <c r="V48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="W48" s="3">
         <v>200</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
       <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
         <v>100</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
-      </c>
       <c r="Z48" s="3">
         <v>0</v>
       </c>
       <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="3">
         <v>800</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4308,8 +4416,11 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4406,8 +4517,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4504,8 +4618,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4602,86 +4719,89 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E52" s="3">
         <v>1000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>300</v>
       </c>
       <c r="H52" s="3">
         <v>300</v>
       </c>
       <c r="I52" s="3">
+        <v>300</v>
+      </c>
+      <c r="J52" s="3">
         <v>5500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10000</v>
-      </c>
-      <c r="R52" s="3">
-        <v>10100</v>
       </c>
       <c r="S52" s="3">
         <v>10100</v>
       </c>
       <c r="T52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="U52" s="3">
         <v>9800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>500</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
       <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
         <v>2400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>200</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4700,8 +4820,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4798,86 +4921,89 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>178300</v>
+      </c>
+      <c r="E54" s="3">
         <v>59000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>82700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>95300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>120900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>147800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>185700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>214600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>212700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>242600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>220100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>245900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>278100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>306500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>317700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>346000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>363700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>380200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>399700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>421300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>432900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>436100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>262400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>103100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>108400</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4896,8 +5022,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4932,8 +5061,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4968,86 +5098,87 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7400</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
       <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
         <v>1400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2000</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5066,52 +5197,55 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E58" s="3">
         <v>7100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1800</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>800</v>
       </c>
       <c r="O58" s="3">
+        <v>800</v>
+      </c>
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>300</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>400</v>
       </c>
       <c r="R58" s="3">
         <v>400</v>
@@ -5129,23 +5263,23 @@
         <v>400</v>
       </c>
       <c r="W58" s="3">
+        <v>400</v>
+      </c>
+      <c r="X58" s="3">
         <v>100</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3">
         <v>2600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>900</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5164,86 +5298,89 @@
       <c r="AH58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>2000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1100</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5262,86 +5399,89 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E60" s="3">
         <v>24600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>38400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>36000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>25200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24000</v>
-      </c>
-      <c r="S60" s="3">
-        <v>15300</v>
       </c>
       <c r="T60" s="3">
         <v>15300</v>
       </c>
       <c r="U60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="V60" s="3">
         <v>12500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4000</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5360,86 +5500,89 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E61" s="3">
         <v>7700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>100</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>3200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4700</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5458,86 +5601,89 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E62" s="3">
         <v>800</v>
-      </c>
-      <c r="E62" s="3">
-        <v>900</v>
       </c>
       <c r="F62" s="3">
         <v>900</v>
       </c>
       <c r="G62" s="3">
+        <v>900</v>
+      </c>
+      <c r="H62" s="3">
         <v>1000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1100</v>
       </c>
       <c r="J62" s="3">
         <v>1100</v>
       </c>
       <c r="K62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L62" s="3">
         <v>1200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>200</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
       <c r="Y62" s="3">
         <v>0</v>
       </c>
       <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
         <v>800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>600</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5556,8 +5702,11 @@
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5654,8 +5803,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5752,8 +5904,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5850,86 +6005,89 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E66" s="3">
         <v>33100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>37900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>30900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>48900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>55300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>48500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>51400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>43000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>30700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>12500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9300</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5948,8 +6106,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5984,8 +6145,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6082,8 +6244,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6180,8 +6345,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6252,13 +6420,13 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="AA70" s="3">
         <v>175000</v>
       </c>
       <c r="AB70" s="3">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="AC70" s="3">
         <v>0</v>
@@ -6278,8 +6446,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6376,86 +6547,89 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-740700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-722800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-700000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-677800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-651900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-621100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-592000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-561300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-521900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-486300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-440800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-389800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-355700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-325500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-294800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-259400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-226500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-202000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-173500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-149000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-132700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-118500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-99700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-89600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-78200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6474,8 +6648,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6572,8 +6749,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6670,8 +6850,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6768,86 +6951,89 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>151300</v>
+      </c>
+      <c r="E76" s="3">
         <v>26000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>44800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>64400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>88300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>113600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>136800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>159300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>164200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>189700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>168800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>212700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>240400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>263500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>287000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>316300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>343600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>363000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>385200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>405000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>418500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>429800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>252000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-84400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-75900</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6866,8 +7052,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6964,209 +7153,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-22800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-22100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-30800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-29200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-30700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-39400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-35600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-45500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-51000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-34200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-30200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-35300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-32900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-24500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-28400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-24600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-16300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-14200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7201,8 +7399,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7231,7 +7430,7 @@
         <v>200</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -7255,7 +7454,7 @@
         <v>100</v>
       </c>
       <c r="T83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -7273,7 +7472,7 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA83" s="3">
         <v>100</v>
@@ -7290,8 +7489,8 @@
       <c r="AE83" s="3">
         <v>100</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
+      <c r="AF83" s="3">
+        <v>100</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
@@ -7299,8 +7498,11 @@
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7397,8 +7599,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7495,8 +7700,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7593,8 +7801,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7691,8 +7902,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7789,106 +8003,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-19000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-17100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-24700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-32000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-25400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-37900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-39700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-31200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-31700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-27800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-30900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-17000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-20700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-17500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-24900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-20600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-13600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-9500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7923,22 +8143,23 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
@@ -7956,35 +8177,35 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
         <v>1300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
@@ -8001,28 +8222,31 @@
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>100</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8119,8 +8343,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8217,68 +8444,71 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E94" s="3">
         <v>11200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>21400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>22300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>27600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>33200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>25700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>26500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>12800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>6200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>42300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>10900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>13700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-76100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-183900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
@@ -8286,37 +8516,40 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>600</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>100</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8351,8 +8584,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8392,8 +8626,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8449,8 +8683,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8547,8 +8784,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8645,8 +8885,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8743,97 +8986,100 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>139600</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-200</v>
       </c>
       <c r="F100" s="3">
         <v>-200</v>
       </c>
       <c r="G100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
-      </c>
-      <c r="H100" s="3">
-        <v>300</v>
       </c>
       <c r="I100" s="3">
         <v>300</v>
       </c>
       <c r="J100" s="3">
+        <v>300</v>
+      </c>
+      <c r="K100" s="3">
         <v>27200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>59200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>188400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>170300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>105000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5900</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>9400</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
+      <c r="AF100" s="3">
+        <v>0</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
@@ -8841,8 +9087,11 @@
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8882,8 +9131,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8939,102 +9188,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-25200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>14400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-92700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-204500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-21500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-24800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-19900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>174700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>161400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>96000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
